--- a/Excel/EquipRedConfig.xlsx
+++ b/Excel/EquipRedConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Quality</t>
+  </si>
+  <si>
     <t>Count</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>生命倍率</t>
   </si>
   <si>
@@ -81,6 +87,24 @@
   </si>
   <si>
     <t>继承比例</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>物伤倍率</t>
+  </si>
+  <si>
+    <t>道攻倍率</t>
+  </si>
+  <si>
+    <t>道伤倍率</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>韧性倍率</t>
   </si>
 </sst>
 </file>
@@ -1038,23 +1062,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:I14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="C1:J50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="16.25" style="1" customWidth="1"/>
-    <col min="6" max="7" width="13.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="16.25" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="9:9">
-      <c r="I1" s="1" t="s">
+    <row r="1" spans="3:10">
+      <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8">
+    <row r="3" ht="13.5" spans="3:10">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1073,10 +1097,13 @@
       <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="3:8">
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" spans="3:10">
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -1093,28 +1120,34 @@
       <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="3:8">
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" spans="3:10">
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1122,22 +1155,25 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
         <v>2003</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>50</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>10</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9">
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1148,19 +1184,22 @@
         <v>6</v>
       </c>
       <c r="F7" s="1">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
         <v>2002</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>50</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>10</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9">
+      <c r="J7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1168,22 +1207,25 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>2011</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>20</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>5</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9">
+      <c r="J8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1191,22 +1233,25 @@
         <v>2</v>
       </c>
       <c r="E9" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
         <v>2008</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>20</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>5</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9">
+      <c r="J9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1217,19 +1262,22 @@
         <v>6</v>
       </c>
       <c r="F10" s="1">
+        <v>6</v>
+      </c>
+      <c r="G10" s="1">
         <v>2005</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>20</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="3:9">
+      <c r="J10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1237,22 +1285,25 @@
         <v>2</v>
       </c>
       <c r="E11" s="1">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1">
         <v>10</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>30</v>
       </c>
-      <c r="G11" s="1">
-        <v>10</v>
-      </c>
       <c r="H11" s="1">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9">
+      <c r="J11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1260,22 +1311,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F12" s="1">
+        <v>2</v>
+      </c>
+      <c r="G12" s="1">
         <v>306</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>1</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9">
+      <c r="I12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1286,19 +1340,22 @@
         <v>6</v>
       </c>
       <c r="F13" s="1">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1">
         <v>307</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>50</v>
       </c>
-      <c r="H13" s="1">
-        <v>10</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="3:9">
+      <c r="I13" s="1">
+        <v>20</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1306,19 +1363,880 @@
         <v>3</v>
       </c>
       <c r="E14" s="1">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1">
         <v>10</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>17</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>10</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>1</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10">
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H16" s="1">
+        <v>20</v>
+      </c>
+      <c r="I16" s="1">
+        <v>20</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
+      <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>7</v>
+      </c>
+      <c r="F17" s="1">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H17" s="1">
+        <v>30</v>
+      </c>
+      <c r="I17" s="1">
+        <v>30</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H18" s="1">
+        <v>40</v>
+      </c>
+      <c r="I18" s="1">
+        <v>40</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H19" s="1">
+        <v>20</v>
+      </c>
+      <c r="I19" s="1">
+        <v>20</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1">
+        <v>6</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H20" s="1">
+        <v>30</v>
+      </c>
+      <c r="I20" s="1">
+        <v>30</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H21" s="1">
+        <v>40</v>
+      </c>
+      <c r="I21" s="1">
+        <v>40</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10">
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H22" s="1">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1">
+        <v>20</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10">
+      <c r="C23" s="1">
         <v>17</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>7</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H23" s="1">
+        <v>30</v>
+      </c>
+      <c r="I23" s="1">
+        <v>30</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10">
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2003</v>
+      </c>
+      <c r="H24" s="1">
+        <v>40</v>
+      </c>
+      <c r="I24" s="1">
+        <v>40</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10">
+      <c r="C26" s="1">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H26" s="1">
+        <v>40</v>
+      </c>
+      <c r="I26" s="1">
+        <v>40</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10">
+      <c r="C27" s="1">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1">
+        <v>6</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H27" s="1">
+        <v>60</v>
+      </c>
+      <c r="I27" s="1">
+        <v>60</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10">
+      <c r="C28" s="1">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1">
+        <v>8</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H28" s="1">
+        <v>80</v>
+      </c>
+      <c r="I28" s="1">
+        <v>80</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10">
+      <c r="C29" s="1">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H29" s="1">
+        <v>40</v>
+      </c>
+      <c r="I29" s="1">
+        <v>40</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10">
+      <c r="C30" s="1">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="1">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H30" s="1">
+        <v>40</v>
+      </c>
+      <c r="I30" s="1">
+        <v>40</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10">
+      <c r="C31" s="1">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H31" s="1">
+        <v>60</v>
+      </c>
+      <c r="I31" s="1">
+        <v>60</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="3:10">
+      <c r="C32" s="1">
+        <v>25</v>
+      </c>
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>8</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H32" s="1">
+        <v>80</v>
+      </c>
+      <c r="I32" s="1">
+        <v>80</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="3:10">
+      <c r="C33" s="1">
+        <v>26</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H33" s="1">
+        <v>40</v>
+      </c>
+      <c r="I33" s="1">
+        <v>40</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10">
+      <c r="C34" s="1">
+        <v>27</v>
+      </c>
+      <c r="D34" s="1">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8</v>
+      </c>
+      <c r="F34" s="1">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H34" s="1">
+        <v>40</v>
+      </c>
+      <c r="I34" s="1">
+        <v>40</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="3:10">
+      <c r="C35" s="1">
+        <v>28</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H35" s="1">
+        <v>60</v>
+      </c>
+      <c r="I35" s="1">
+        <v>60</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10">
+      <c r="C36" s="1">
+        <v>29</v>
+      </c>
+      <c r="D36" s="1">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1">
+        <v>8</v>
+      </c>
+      <c r="F36" s="1">
+        <v>8</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H36" s="1">
+        <v>80</v>
+      </c>
+      <c r="I36" s="1">
+        <v>80</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="3:10">
+      <c r="C37" s="1">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+      <c r="F37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H37" s="1">
+        <v>40</v>
+      </c>
+      <c r="I37" s="1">
+        <v>40</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="3:10">
+      <c r="C39" s="1">
+        <v>31</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>9</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H39" s="1">
+        <v>60</v>
+      </c>
+      <c r="I39" s="1">
+        <v>60</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10">
+      <c r="C40" s="1">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>9</v>
+      </c>
+      <c r="F40" s="1">
+        <v>6</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H40" s="1">
+        <v>90</v>
+      </c>
+      <c r="I40" s="1">
+        <v>90</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="3:10">
+      <c r="C41" s="1">
+        <v>33</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1">
+        <v>8</v>
+      </c>
+      <c r="G41" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H41" s="1">
+        <v>120</v>
+      </c>
+      <c r="I41" s="1">
+        <v>120</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10">
+      <c r="C42" s="1">
+        <v>34</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H42" s="1">
+        <v>60</v>
+      </c>
+      <c r="I42" s="1">
+        <v>60</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="3:10">
+      <c r="C43" s="1">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>9</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2005</v>
+      </c>
+      <c r="H43" s="1">
+        <v>60</v>
+      </c>
+      <c r="I43" s="1">
+        <v>60</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10">
+      <c r="C44" s="1">
+        <v>36</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>9</v>
+      </c>
+      <c r="F44" s="1">
+        <v>6</v>
+      </c>
+      <c r="G44" s="1">
+        <v>2008</v>
+      </c>
+      <c r="H44" s="1">
+        <v>90</v>
+      </c>
+      <c r="I44" s="1">
+        <v>90</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="3:10">
+      <c r="C45" s="1">
+        <v>37</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>9</v>
+      </c>
+      <c r="F45" s="1">
+        <v>8</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H45" s="1">
+        <v>120</v>
+      </c>
+      <c r="I45" s="1">
+        <v>120</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="3:10">
+      <c r="C46" s="1">
+        <v>38</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>9</v>
+      </c>
+      <c r="F46" s="1">
+        <v>10</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H46" s="1">
+        <v>60</v>
+      </c>
+      <c r="I46" s="1">
+        <v>60</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="3:10">
+      <c r="C47" s="1">
+        <v>39</v>
+      </c>
+      <c r="D47" s="1">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1">
+        <v>9</v>
+      </c>
+      <c r="F47" s="1">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H47" s="1">
+        <v>60</v>
+      </c>
+      <c r="I47" s="1">
+        <v>60</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="3:10">
+      <c r="C48" s="1">
+        <v>40</v>
+      </c>
+      <c r="D48" s="1">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1">
+        <v>9</v>
+      </c>
+      <c r="F48" s="1">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2009</v>
+      </c>
+      <c r="H48" s="1">
+        <v>90</v>
+      </c>
+      <c r="I48" s="1">
+        <v>90</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10">
+      <c r="C49" s="1">
+        <v>41</v>
+      </c>
+      <c r="D49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>9</v>
+      </c>
+      <c r="F49" s="1">
+        <v>8</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H49" s="1">
+        <v>120</v>
+      </c>
+      <c r="I49" s="1">
+        <v>120</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="3:10">
+      <c r="C50" s="1">
+        <v>42</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="E50" s="1">
+        <v>9</v>
+      </c>
+      <c r="F50" s="1">
+        <v>10</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2012</v>
+      </c>
+      <c r="H50" s="1">
+        <v>60</v>
+      </c>
+      <c r="I50" s="1">
+        <v>60</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
